--- a/outputs/licence_report_report.xlsx
+++ b/outputs/licence_report_report.xlsx
@@ -1292,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1358,24 +1358,39 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Advent</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>User_input</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Sum of all</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="12" t="inlineStr"/>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="C7" s="8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="8" customHeight="1">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1392,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1472,19 +1487,30 @@
       <c r="C7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Advent</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" ht="8" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="B9" s="8" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1647,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1704,18 +1730,16 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>pp</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>feefawg</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>User Input</t>
-        </is>
+          <t>KEY_001</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1731,53 +1755,24 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>pp</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>KEY_001</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>User Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Autocad</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>sp3d</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>VEC</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>gdsfbgsfdb</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>User Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1">
-      <c r="A6" s="12" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="12" t="inlineStr"/>
+          <t>feefawg</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="8" customHeight="1">
+      <c r="A5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr"/>
+      <c r="C5" s="12" t="inlineStr"/>
+      <c r="D5" s="12" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
